--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D991FA3-09C5-4183-B0ED-251389945260}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="38" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="38" t="s">
@@ -6616,7 +6616,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="39" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="39" t="s">
@@ -6634,7 +6634,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="42"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="38" t="s">
         <v>40</v>
       </c>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="42"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="39" t="s">
         <v>48</v>
       </c>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="42"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="41" t="s">
         <v>40</v>
       </c>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
-      <c r="B30" s="43"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="43" t="s">
         <v>50</v>
       </c>
@@ -8342,13 +8342,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A20AAC2-369B-4699-8644-4367F4F0E3A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A670DFB3-4E88-4AF2-B690-D1C73746BF68}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E103B2-006F-47F4-8EFF-D92C4A239073}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B70CBE5F-0055-4F1B-9CB9-7149C52E83D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889D4AA-2256-47B4-B8F5-7358D1D49ED3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3632A59-1026-4BBC-90EB-ED690FF88C9C}"/>
 </file>
--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D991FA3-09C5-4183-B0ED-251389945260}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="41" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="38" t="s">
@@ -6616,7 +6616,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="42" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="39" t="s">
@@ -6634,7 +6634,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="39"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="38" t="s">
         <v>40</v>
       </c>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="39"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="39" t="s">
         <v>48</v>
       </c>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="41" t="s">
         <v>40</v>
       </c>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="43" t="s">
         <v>50</v>
       </c>
@@ -8342,13 +8342,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A670DFB3-4E88-4AF2-B690-D1C73746BF68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A20AAC2-369B-4699-8644-4367F4F0E3A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B70CBE5F-0055-4F1B-9CB9-7149C52E83D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E103B2-006F-47F4-8EFF-D92C4A239073}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3632A59-1026-4BBC-90EB-ED690FF88C9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889D4AA-2256-47B4-B8F5-7358D1D49ED3}"/>
 </file>
--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D991FA3-09C5-4183-B0ED-251389945260}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0A8EF12-C27E-489D-A5EC-0FEAFD781CA7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -246,9 +246,6 @@
     <t>17:30/21:00</t>
   </si>
   <si>
-    <t>16:30/24:00</t>
-  </si>
-  <si>
     <t>15:30/16:30</t>
   </si>
   <si>
@@ -406,6 +403,9 @@
   </si>
   <si>
     <t>EDF // ANNIV // PADEL U14</t>
+  </si>
+  <si>
+    <t>16:30/22:00</t>
   </si>
 </sst>
 </file>
@@ -6239,22 +6239,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="D3" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="F3" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>126</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>127</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>13</v>
@@ -6476,7 +6476,7 @@
       <c r="A17" s="25"/>
       <c r="B17" s="3"/>
       <c r="C17" s="55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="3"/>
@@ -6522,7 +6522,7 @@
       <c r="A20" s="25"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
@@ -7014,10 +7014,10 @@
         <v>73</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="39" t="s">
         <v>74</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>75</v>
       </c>
       <c r="E52" s="42" t="s">
         <v>49</v>
@@ -7049,14 +7049,14 @@
       <c r="B54" s="42"/>
       <c r="C54" s="3"/>
       <c r="D54" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="39" t="s">
         <v>77</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>78</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H54" s="26"/>
     </row>
@@ -7078,7 +7078,7 @@
       <c r="C56" s="28"/>
       <c r="D56" s="43"/>
       <c r="E56" s="43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
@@ -7086,7 +7086,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -7140,7 +7140,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -7190,7 +7190,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -7211,12 +7211,12 @@
       <c r="F66" s="28"/>
       <c r="G66" s="28"/>
       <c r="H66" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -7268,7 +7268,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" s="57" t="s">
         <v>59</v>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -7343,7 +7343,7 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7367,12 +7367,12 @@
       <c r="F78" s="28"/>
       <c r="G78" s="28"/>
       <c r="H78" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B79" s="22"/>
       <c r="C79" s="44" t="s">
@@ -7422,7 +7422,7 @@
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="19"/>
@@ -7434,7 +7434,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B84" s="22" t="s">
         <v>12</v>
@@ -7444,13 +7444,13 @@
         <v>12</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F84" s="22" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H84" s="24"/>
     </row>
@@ -7461,16 +7461,16 @@
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G85" s="42" t="s">
         <v>97</v>
-      </c>
-      <c r="G85" s="42" t="s">
-        <v>98</v>
       </c>
       <c r="H85" s="26"/>
     </row>
@@ -7481,7 +7481,7 @@
       <c r="D86" s="30"/>
       <c r="E86" s="3"/>
       <c r="F86" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>12</v>
@@ -7495,16 +7495,16 @@
       <c r="D87" s="28"/>
       <c r="E87" s="28"/>
       <c r="F87" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G87" s="28" t="s">
         <v>99</v>
-      </c>
-      <c r="G87" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="H87" s="29"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -7524,7 +7524,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H89" s="26"/>
     </row>
@@ -7548,13 +7548,13 @@
       <c r="E91" s="28"/>
       <c r="F91" s="28"/>
       <c r="G91" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="19"/>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -7639,16 +7639,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7840,7 +7840,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -7891,7 +7891,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -7908,7 +7908,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -7942,7 +7942,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -8010,7 +8010,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -8027,7 +8027,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -8128,40 +8128,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -8342,13 +8342,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A670DFB3-4E88-4AF2-B690-D1C73746BF68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C5BFC3-985A-4BC3-A219-38137A130FC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B70CBE5F-0055-4F1B-9CB9-7149C52E83D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C674F3C6-463B-4A2D-B5F9-8DCACE2C92F8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3632A59-1026-4BBC-90EB-ED690FF88C9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9005B47A-C290-4C74-87E4-D7C46FC4C36E}"/>
 </file>
--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0A8EF12-C27E-489D-A5EC-0FEAFD781CA7}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D96D932-A4D0-4CB3-B223-B98C5D5291D3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
   <si>
     <t>Planning des salariés du 09/11/2026 au 15/11/2026</t>
   </si>
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t>16:30/22:00</t>
+  </si>
+  <si>
+    <t>10:15/13:45</t>
   </si>
 </sst>
 </file>
@@ -1483,50 +1486,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
@@ -5828,6 +5787,138 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7037294" y="9076765"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{383F3EFD-15F7-448E-B198-B1F6A97BA721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9470571" y="2735036"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D565FA4-3512-44E9-B7AE-DC96CDAEDFB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12627429" y="2735036"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B02E6-5F90-4057-9223-DB9B49CF29AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3156857" y="2735036"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6430,14 +6521,12 @@
       <c r="A15" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="B15" s="22"/>
       <c r="C15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="44" t="s">
-        <v>19</v>
+      <c r="D15" s="22" t="s">
+        <v>12</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>12</v>
@@ -6452,14 +6541,12 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
-      <c r="B16" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="42" t="s">
-        <v>20</v>
+      <c r="D16" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>14</v>
@@ -6478,7 +6565,9 @@
       <c r="C17" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="54"/>
+      <c r="D17" s="41" t="s">
+        <v>19</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="2" t="s">
         <v>12</v>
@@ -6492,7 +6581,9 @@
       <c r="C18" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="43"/>
+      <c r="D18" s="42" t="s">
+        <v>20</v>
+      </c>
       <c r="E18" s="28"/>
       <c r="F18" s="28" t="s">
         <v>32</v>
@@ -6504,7 +6595,9 @@
       <c r="A19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="C19" s="22" t="s">
         <v>12</v>
       </c>
@@ -6520,7 +6613,9 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>127</v>
       </c>
@@ -8342,13 +8437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C5BFC3-985A-4BC3-A219-38137A130FC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F6020A0-F63C-486D-A5FE-37D8A15F31E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C674F3C6-463B-4A2D-B5F9-8DCACE2C92F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0343F4D2-954A-423C-9C16-BA72826BA897}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9005B47A-C290-4C74-87E4-D7C46FC4C36E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55905A8-608B-4721-AD67-071761F9B7D9}"/>
 </file>
--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D96D932-A4D0-4CB3-B223-B98C5D5291D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3140DCD-9426-4C32-8EE9-BB8F9EFFEED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="128">
   <si>
     <t>Planning des salariés du 09/11/2026 au 15/11/2026</t>
   </si>
@@ -246,6 +246,9 @@
     <t>17:30/21:00</t>
   </si>
   <si>
+    <t>16:30/24:00</t>
+  </si>
+  <si>
     <t>15:30/16:30</t>
   </si>
   <si>
@@ -403,12 +406,6 @@
   </si>
   <si>
     <t>EDF // ANNIV // PADEL U14</t>
-  </si>
-  <si>
-    <t>16:30/22:00</t>
-  </si>
-  <si>
-    <t>10:15/13:45</t>
   </si>
 </sst>
 </file>
@@ -1486,6 +1483,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
@@ -5787,138 +5828,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7037294" y="9076765"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{383F3EFD-15F7-448E-B198-B1F6A97BA721}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9470571" y="2735036"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D565FA4-3512-44E9-B7AE-DC96CDAEDFB2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12627429" y="2735036"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{286B02E6-5F90-4057-9223-DB9B49CF29AF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3156857" y="2735036"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6330,22 +6239,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>13</v>
@@ -6521,12 +6430,14 @@
       <c r="A15" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="C15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>12</v>
+      <c r="D15" s="44" t="s">
+        <v>19</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>12</v>
@@ -6541,12 +6452,14 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>128</v>
+      <c r="D16" s="42" t="s">
+        <v>20</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>14</v>
@@ -6563,11 +6476,9 @@
       <c r="A17" s="25"/>
       <c r="B17" s="3"/>
       <c r="C17" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>19</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D17" s="54"/>
       <c r="E17" s="3"/>
       <c r="F17" s="2" t="s">
         <v>12</v>
@@ -6581,9 +6492,7 @@
       <c r="C18" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="42" t="s">
-        <v>20</v>
-      </c>
+      <c r="D18" s="43"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28" t="s">
         <v>32</v>
@@ -6595,9 +6504,7 @@
       <c r="A19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="B19" s="22"/>
       <c r="C19" s="22" t="s">
         <v>12</v>
       </c>
@@ -6613,11 +6520,9 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
-      <c r="B20" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
@@ -6693,7 +6598,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="41" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="38" t="s">
@@ -6711,7 +6616,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="42" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="39" t="s">
@@ -6729,7 +6634,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
-      <c r="B27" s="39"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="38" t="s">
         <v>40</v>
       </c>
@@ -6743,7 +6648,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
-      <c r="B28" s="39"/>
+      <c r="B28" s="42"/>
       <c r="C28" s="39" t="s">
         <v>48</v>
       </c>
@@ -6757,7 +6662,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="41" t="s">
         <v>40</v>
       </c>
@@ -6771,7 +6676,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="43" t="s">
         <v>50</v>
       </c>
@@ -7109,10 +7014,10 @@
         <v>73</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E52" s="42" t="s">
         <v>49</v>
@@ -7144,14 +7049,14 @@
       <c r="B54" s="42"/>
       <c r="C54" s="3"/>
       <c r="D54" s="42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" s="26"/>
     </row>
@@ -7173,7 +7078,7 @@
       <c r="C56" s="28"/>
       <c r="D56" s="43"/>
       <c r="E56" s="43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
@@ -7181,7 +7086,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -7235,7 +7140,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -7285,7 +7190,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -7306,12 +7211,12 @@
       <c r="F66" s="28"/>
       <c r="G66" s="28"/>
       <c r="H66" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -7337,7 +7242,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -7363,7 +7268,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B71" s="57" t="s">
         <v>59</v>
@@ -7393,7 +7298,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -7438,7 +7343,7 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -7462,12 +7367,12 @@
       <c r="F78" s="28"/>
       <c r="G78" s="28"/>
       <c r="H78" s="51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B79" s="22"/>
       <c r="C79" s="44" t="s">
@@ -7517,7 +7422,7 @@
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="19"/>
@@ -7529,7 +7434,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B84" s="22" t="s">
         <v>12</v>
@@ -7539,13 +7444,13 @@
         <v>12</v>
       </c>
       <c r="E84" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F84" s="22" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H84" s="24"/>
     </row>
@@ -7556,16 +7461,16 @@
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G85" s="42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H85" s="26"/>
     </row>
@@ -7576,7 +7481,7 @@
       <c r="D86" s="30"/>
       <c r="E86" s="3"/>
       <c r="F86" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>12</v>
@@ -7590,16 +7495,16 @@
       <c r="D87" s="28"/>
       <c r="E87" s="28"/>
       <c r="F87" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H87" s="29"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -7619,7 +7524,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H89" s="26"/>
     </row>
@@ -7643,13 +7548,13 @@
       <c r="E91" s="28"/>
       <c r="F91" s="28"/>
       <c r="G91" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H91" s="29"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="19"/>
@@ -7715,7 +7620,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -7723,7 +7628,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -7734,16 +7639,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7935,7 +7840,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
@@ -7952,7 +7857,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>0</v>
@@ -7969,7 +7874,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="8">
         <v>0</v>
@@ -7986,7 +7891,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="8">
         <v>0</v>
@@ -8003,7 +7908,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="8">
         <v>0</v>
@@ -8020,7 +7925,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="8">
         <v>0</v>
@@ -8037,7 +7942,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
@@ -8054,7 +7959,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
@@ -8071,7 +7976,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
@@ -8088,7 +7993,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
@@ -8105,7 +8010,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="8">
         <v>0</v>
@@ -8122,7 +8027,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B29" s="8">
         <v>0</v>
@@ -8139,7 +8044,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" s="8">
         <v>0</v>
@@ -8156,7 +8061,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B31" s="8">
         <v>0</v>
@@ -8173,7 +8078,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B32" s="8">
         <v>0</v>
@@ -8223,40 +8128,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -8437,13 +8342,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F6020A0-F63C-486D-A5FE-37D8A15F31E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A20AAC2-369B-4699-8644-4367F4F0E3A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0343F4D2-954A-423C-9C16-BA72826BA897}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E103B2-006F-47F4-8EFF-D92C4A239073}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55905A8-608B-4721-AD67-071761F9B7D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C889D4AA-2256-47B4-B8F5-7358D1D49ED3}"/>
 </file>
--- a/Plannings 2026 S46.xlsx
+++ b/Plannings 2026 S46.xlsx
@@ -8437,13 +8437,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F6020A0-F63C-486D-A5FE-37D8A15F31E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33251810-0FDB-4BD1-84C0-F0BD55218925}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0343F4D2-954A-423C-9C16-BA72826BA897}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4D41533-5A19-40B1-AFBC-7C3EFE9491C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55905A8-608B-4721-AD67-071761F9B7D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C28E8E0-146D-478F-8E5A-C64BEAD32EED}"/>
 </file>